--- a/artfynd/A 30071-2025 artfynd.xlsx
+++ b/artfynd/A 30071-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>5209231</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>Russås, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353397.2554263781</v>
+        <v>353397</v>
       </c>
       <c r="R2" t="n">
-        <v>6617978.897800341</v>
+        <v>6617979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
